--- a/资产负债表.xlsx
+++ b/资产负债表.xlsx
@@ -2216,749 +2216,773 @@
         <v>170002.188810001</v>
       </c>
     </row>
-    <row r="17" spans="2:20">
+    <row r="17" spans="1:20">
+      <c r="A17" s="1">
+        <v>46295</v>
+      </c>
       <c r="B17" s="2">
         <f t="shared" si="7"/>
-        <v>3439907</v>
+        <v>3440676.04</v>
+      </c>
+      <c r="C17" s="2">
+        <v>3776024.9</v>
       </c>
       <c r="D17" s="2">
-        <v>0</v>
+        <v>769.04</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="0"/>
-        <v>-3439907</v>
+        <v>335348.859999998</v>
+      </c>
+      <c r="F17" s="2">
+        <v>151026.62</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="8"/>
         <v>3382.11</v>
       </c>
+      <c r="H17" s="2">
+        <v>28283.94</v>
+      </c>
       <c r="I17" s="2">
         <v>0</v>
       </c>
       <c r="J17" s="2">
         <f t="shared" si="1"/>
+        <v>24901.83</v>
+      </c>
+      <c r="K17" s="2">
+        <v>11</v>
+      </c>
+      <c r="L17" s="3">
+        <v>6.7069</v>
+      </c>
+      <c r="M17" s="2">
+        <f t="shared" si="2"/>
+        <v>189697.557186</v>
+      </c>
+      <c r="N17" s="2">
+        <f t="shared" si="3"/>
+        <v>167014.083627</v>
+      </c>
+      <c r="O17" s="2">
+        <f t="shared" si="4"/>
+        <v>502362.943626998</v>
+      </c>
+      <c r="P17" s="2">
+        <v>3034500</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>21100</v>
+      </c>
+      <c r="R17" s="2">
+        <f t="shared" si="5"/>
+        <v>3965722.457186</v>
+      </c>
+      <c r="S17" s="2">
+        <f t="shared" si="6"/>
+        <v>952322.457186</v>
+      </c>
+      <c r="T17" s="2">
+        <f t="shared" si="9"/>
+        <v>-316843.656076001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="B18" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G18" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M17" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R17" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S17" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T17" s="2">
-        <f t="shared" si="9"/>
-        <v>-1269166.113262</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20">
-      <c r="B18" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G18" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2">
+      <c r="M18" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R18" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="2">
+        <f t="shared" si="9"/>
+        <v>-952322.457186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
+      <c r="B19" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G19" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M18" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R18" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20">
-      <c r="B19" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G19" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2">
+      <c r="M19" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R19" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="B20" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G20" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M19" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R19" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T19" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:20">
-      <c r="B20" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G20" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2">
+      <c r="M20" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R20" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="B21" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G21" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M20" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R20" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T20" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20">
-      <c r="B21" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0</v>
-      </c>
-      <c r="E21" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G21" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
+      <c r="M21" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R21" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
+      <c r="B22" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G22" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M21" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R21" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T21" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20">
-      <c r="B22" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G22" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
+      <c r="M22" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R22" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
+      <c r="B23" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G23" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M22" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R22" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S22" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T22" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:20">
-      <c r="B23" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0</v>
-      </c>
-      <c r="E23" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G23" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2">
+      <c r="M23" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R23" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
+      <c r="B24" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M23" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R23" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S23" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T23" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:20">
-      <c r="B24" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D24" s="2">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G24" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2">
+      <c r="M24" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R24" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
+      <c r="B25" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M24" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N24" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R24" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S24" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T24" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20">
-      <c r="B25" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D25" s="2">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G25" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2">
+      <c r="M25" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R25" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
+      <c r="B26" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G26" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M25" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O25" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R25" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S25" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T25" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20">
-      <c r="B26" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D26" s="2">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G26" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2">
+      <c r="M26" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R26" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
+      <c r="B27" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G27" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M26" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R26" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:20">
-      <c r="B27" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D27" s="2">
-        <v>0</v>
-      </c>
-      <c r="E27" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G27" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2">
+      <c r="M27" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R27" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
+      <c r="B28" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G28" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M27" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N27" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O27" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R27" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T27" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:20">
-      <c r="B28" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D28" s="2">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G28" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2">
+      <c r="M28" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R28" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
+      <c r="B29" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G29" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M28" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N28" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R28" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T28" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:20">
-      <c r="B29" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D29" s="2">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G29" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2">
+      <c r="M29" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O29" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R29" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="B30" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G30" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M29" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R29" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S29" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T29" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:20">
-      <c r="B30" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D30" s="2">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G30" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2">
+      <c r="M30" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R30" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
+      <c r="B31" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G31" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M30" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N30" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O30" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R30" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S30" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T30" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:20">
-      <c r="B31" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D31" s="2">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G31" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I31" s="2">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2">
+      <c r="M31" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O31" s="2">
+        <f t="shared" si="4"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="R31" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
+      <c r="B32" s="2">
+        <f t="shared" si="7"/>
+        <v>3440676.04</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2">
+        <f t="shared" si="0"/>
+        <v>-3440676.04</v>
+      </c>
+      <c r="G32" s="2">
+        <f t="shared" si="8"/>
+        <v>3382.11</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2">
         <f t="shared" si="1"/>
         <v>-3382.11</v>
       </c>
-      <c r="M31" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N31" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O31" s="2">
-        <f t="shared" si="4"/>
-        <v>-3439907</v>
-      </c>
-      <c r="R31" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T31" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:20">
-      <c r="B32" s="2">
-        <f t="shared" si="7"/>
-        <v>3439907</v>
-      </c>
-      <c r="D32" s="2">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2">
-        <f t="shared" si="0"/>
-        <v>-3439907</v>
-      </c>
-      <c r="G32" s="2">
-        <f t="shared" si="8"/>
-        <v>3382.11</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2">
-        <f t="shared" si="1"/>
-        <v>-3382.11</v>
-      </c>
       <c r="M32" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2969,7 +2993,7 @@
       </c>
       <c r="O32" s="2">
         <f t="shared" si="4"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="R32" s="2">
         <f t="shared" si="5"/>
@@ -2987,14 +3011,14 @@
     <row r="33" spans="2:20">
       <c r="B33" s="2">
         <f t="shared" si="7"/>
-        <v>3439907</v>
+        <v>3440676.04</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2">
         <f t="shared" si="0"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="G33" s="2">
         <f t="shared" si="8"/>
@@ -3017,7 +3041,7 @@
       </c>
       <c r="O33" s="2">
         <f t="shared" si="4"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="R33" s="2">
         <f t="shared" si="5"/>
@@ -3035,14 +3059,14 @@
     <row r="34" spans="2:20">
       <c r="B34" s="2">
         <f t="shared" si="7"/>
-        <v>3439907</v>
+        <v>3440676.04</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2">
         <f t="shared" si="0"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="G34" s="2">
         <f t="shared" si="8"/>
@@ -3065,7 +3089,7 @@
       </c>
       <c r="O34" s="2">
         <f t="shared" si="4"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="R34" s="2">
         <f t="shared" si="5"/>
@@ -3083,14 +3107,14 @@
     <row r="35" spans="2:20">
       <c r="B35" s="2">
         <f t="shared" si="7"/>
-        <v>3439907</v>
+        <v>3440676.04</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2">
         <f t="shared" si="0"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="G35" s="2">
         <f t="shared" si="8"/>
@@ -3113,7 +3137,7 @@
       </c>
       <c r="O35" s="2">
         <f t="shared" si="4"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="R35" s="2">
         <f t="shared" si="5"/>
@@ -3131,14 +3155,14 @@
     <row r="36" spans="2:20">
       <c r="B36" s="2">
         <f t="shared" si="7"/>
-        <v>3439907</v>
+        <v>3440676.04</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2">
         <f t="shared" si="0"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="G36" s="2">
         <f t="shared" si="8"/>
@@ -3161,7 +3185,7 @@
       </c>
       <c r="O36" s="2">
         <f t="shared" si="4"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="R36" s="2">
         <f t="shared" si="5"/>
@@ -3179,14 +3203,14 @@
     <row r="37" spans="2:20">
       <c r="B37" s="2">
         <f t="shared" si="7"/>
-        <v>3439907</v>
+        <v>3440676.04</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="0"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="G37" s="2">
         <f t="shared" si="8"/>
@@ -3209,7 +3233,7 @@
       </c>
       <c r="O37" s="2">
         <f t="shared" si="4"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="R37" s="2">
         <f t="shared" si="5"/>
@@ -3227,14 +3251,14 @@
     <row r="38" spans="2:20">
       <c r="B38" s="2">
         <f t="shared" si="7"/>
-        <v>3439907</v>
+        <v>3440676.04</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2">
         <f t="shared" si="0"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="G38" s="2">
         <f t="shared" si="8"/>
@@ -3257,7 +3281,7 @@
       </c>
       <c r="O38" s="2">
         <f t="shared" si="4"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="R38" s="2">
         <f t="shared" si="5"/>
@@ -3275,14 +3299,14 @@
     <row r="39" spans="2:20">
       <c r="B39" s="2">
         <f t="shared" si="7"/>
-        <v>3439907</v>
+        <v>3440676.04</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="0"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="8"/>
@@ -3305,7 +3329,7 @@
       </c>
       <c r="O39" s="2">
         <f t="shared" si="4"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="R39" s="2">
         <f t="shared" si="5"/>
@@ -3323,14 +3347,14 @@
     <row r="40" spans="2:20">
       <c r="B40" s="2">
         <f t="shared" si="7"/>
-        <v>3439907</v>
+        <v>3440676.04</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2">
         <f t="shared" si="0"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="G40" s="2">
         <f t="shared" si="8"/>
@@ -3353,7 +3377,7 @@
       </c>
       <c r="O40" s="2">
         <f t="shared" si="4"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="R40" s="2">
         <f t="shared" si="5"/>
@@ -3371,14 +3395,14 @@
     <row r="41" spans="2:20">
       <c r="B41" s="2">
         <f t="shared" si="7"/>
-        <v>3439907</v>
+        <v>3440676.04</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2">
         <f t="shared" si="0"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="G41" s="2">
         <f t="shared" si="8"/>
@@ -3401,7 +3425,7 @@
       </c>
       <c r="O41" s="2">
         <f t="shared" si="4"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="R41" s="2">
         <f t="shared" si="5"/>
@@ -3419,14 +3443,14 @@
     <row r="42" spans="2:20">
       <c r="B42" s="2">
         <f t="shared" si="7"/>
-        <v>3439907</v>
+        <v>3440676.04</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" si="0"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="G42" s="2">
         <f t="shared" si="8"/>
@@ -3449,7 +3473,7 @@
       </c>
       <c r="O42" s="2">
         <f t="shared" si="4"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="R42" s="2">
         <f t="shared" si="5"/>
@@ -3467,14 +3491,14 @@
     <row r="43" spans="2:20">
       <c r="B43" s="2">
         <f t="shared" si="7"/>
-        <v>3439907</v>
+        <v>3440676.04</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" si="0"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="G43" s="2">
         <f t="shared" si="8"/>
@@ -3497,7 +3521,7 @@
       </c>
       <c r="O43" s="2">
         <f t="shared" si="4"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="R43" s="2">
         <f t="shared" si="5"/>
@@ -3515,14 +3539,14 @@
     <row r="44" spans="2:20">
       <c r="B44" s="2">
         <f t="shared" si="7"/>
-        <v>3439907</v>
+        <v>3440676.04</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" si="0"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="G44" s="2">
         <f t="shared" si="8"/>
@@ -3545,7 +3569,7 @@
       </c>
       <c r="O44" s="2">
         <f t="shared" si="4"/>
-        <v>-3439907</v>
+        <v>-3440676.04</v>
       </c>
       <c r="R44" s="2">
         <f t="shared" si="5"/>
